--- a/Sindhi Muslim/Student Attendance/Class 2/Class 2 - Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/Class 2/Class 2 - Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\Class 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DB2535-D9E1-449D-BEC9-A2430F98B46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139BA972-2470-40CD-BF48-E4153CD5158F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="123">
   <si>
     <t>S.No</t>
   </si>
@@ -395,9 +395,6 @@
   </si>
   <si>
     <t>IQBAL DAY - IQBAL DAY</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Muhammad Ali</t>
@@ -638,7 +635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -687,17 +684,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="255"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -720,16 +723,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -741,25 +738,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -801,6 +785,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1343,101 +1334,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
+      <c r="A2" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="27" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1560,25 +1551,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AJ3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="24" t="s">
+      <c r="AL3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="25"/>
+      <c r="AM3" s="26"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="19">
         <v>45597</v>
       </c>
@@ -1669,8 +1660,8 @@
       <c r="AI4" s="19">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1700,7 +1691,7 @@
       <c r="G5" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="29" t="s">
         <v>118</v>
       </c>
       <c r="I5" s="20" t="s">
@@ -1718,10 +1709,10 @@
       <c r="M5" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="O5" s="29" t="s">
         <v>118</v>
       </c>
       <c r="P5" s="9" t="s">
@@ -1734,7 +1725,7 @@
         <v>113</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>113</v>
@@ -1742,31 +1733,55 @@
       <c r="U5" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="V5" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="27" t="s">
+      <c r="W5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC5" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
+      <c r="AD5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ5" s="5">
         <f t="shared" ref="AJ5:AJ30" si="1">COUNTIF(F5:AI5,"P")</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK30" si="2">COUNTIF(F5:AI5,"A")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>8</v>
@@ -1799,7 +1814,7 @@
       <c r="G6" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="28"/>
+      <c r="H6" s="30"/>
       <c r="I6" s="20" t="s">
         <v>113</v>
       </c>
@@ -1815,8 +1830,8 @@
       <c r="M6" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N6" s="31"/>
-      <c r="O6" s="28"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="30"/>
       <c r="P6" s="9" t="s">
         <v>113</v>
       </c>
@@ -1835,27 +1850,51 @@
       <c r="U6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V6" s="28"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ6" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>10</v>
@@ -1886,7 +1925,7 @@
       <c r="G7" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H7" s="28"/>
+      <c r="H7" s="30"/>
       <c r="I7" s="20" t="s">
         <v>113</v>
       </c>
@@ -1902,8 +1941,8 @@
       <c r="M7" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N7" s="31"/>
-      <c r="O7" s="28"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="9" t="s">
         <v>113</v>
       </c>
@@ -1922,23 +1961,47 @@
       <c r="U7" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V7" s="28"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="22"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ7" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
@@ -1969,7 +2032,7 @@
       <c r="G8" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="30"/>
       <c r="I8" s="20" t="s">
         <v>115</v>
       </c>
@@ -1985,8 +2048,8 @@
       <c r="M8" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="31"/>
-      <c r="O8" s="28"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="30"/>
       <c r="P8" s="9" t="s">
         <v>115</v>
       </c>
@@ -2005,34 +2068,58 @@
       <c r="U8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="V8" s="28"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-      <c r="AF8" s="22"/>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
-      <c r="AI8" s="9"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG8" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH8" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ8" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AL8" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="25"/>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="26"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="28"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
@@ -2054,7 +2141,7 @@
       <c r="G9" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="20" t="s">
         <v>113</v>
       </c>
@@ -2070,8 +2157,8 @@
       <c r="M9" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N9" s="31"/>
-      <c r="O9" s="28"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="30"/>
       <c r="P9" s="9" t="s">
         <v>113</v>
       </c>
@@ -2090,27 +2177,51 @@
       <c r="U9" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V9" s="28"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
-      <c r="AI9" s="9"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ9" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>12</v>
@@ -2145,7 +2256,7 @@
       <c r="G10" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="30"/>
       <c r="I10" s="20" t="s">
         <v>114</v>
       </c>
@@ -2161,8 +2272,8 @@
       <c r="M10" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N10" s="31"/>
-      <c r="O10" s="28"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="30"/>
       <c r="P10" s="9" t="s">
         <v>114</v>
       </c>
@@ -2181,27 +2292,51 @@
       <c r="U10" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V10" s="28"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="9"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="9"/>
-      <c r="AH10" s="9"/>
-      <c r="AI10" s="9"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA10" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG10" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI10" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ10" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>16</v>
@@ -2239,7 +2374,7 @@
       <c r="G11" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="30"/>
       <c r="I11" s="20" t="s">
         <v>114</v>
       </c>
@@ -2255,8 +2390,8 @@
       <c r="M11" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="N11" s="31"/>
-      <c r="O11" s="28"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="30"/>
       <c r="P11" s="9" t="s">
         <v>114</v>
       </c>
@@ -2275,27 +2410,51 @@
       <c r="U11" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V11" s="28"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="9"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI11" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ11" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>17</v>
@@ -2333,7 +2492,7 @@
       <c r="G12" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="30"/>
       <c r="I12" s="20" t="s">
         <v>113</v>
       </c>
@@ -2349,8 +2508,8 @@
       <c r="M12" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N12" s="31"/>
-      <c r="O12" s="28"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="30"/>
       <c r="P12" s="9" t="s">
         <v>113</v>
       </c>
@@ -2369,23 +2528,47 @@
       <c r="U12" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V12" s="28"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="9"/>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="9"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI12" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ12" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
@@ -2427,7 +2610,7 @@
       <c r="G13" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="30"/>
       <c r="I13" s="20" t="s">
         <v>113</v>
       </c>
@@ -2443,8 +2626,8 @@
       <c r="M13" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N13" s="31"/>
-      <c r="O13" s="28"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="30"/>
       <c r="P13" s="9" t="s">
         <v>113</v>
       </c>
@@ -2463,23 +2646,47 @@
       <c r="U13" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V13" s="28"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="9"/>
-      <c r="AH13" s="9"/>
-      <c r="AI13" s="9"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC13" s="30"/>
+      <c r="AD13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI13" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ13" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
@@ -2510,7 +2717,7 @@
       <c r="G14" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="30"/>
       <c r="I14" s="20" t="s">
         <v>113</v>
       </c>
@@ -2526,8 +2733,8 @@
       <c r="M14" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N14" s="31"/>
-      <c r="O14" s="28"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="30"/>
       <c r="P14" s="9" t="s">
         <v>114</v>
       </c>
@@ -2546,23 +2753,47 @@
       <c r="U14" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V14" s="28"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="9"/>
-      <c r="AH14" s="9"/>
-      <c r="AI14" s="9"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI14" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ14" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
@@ -2593,7 +2824,7 @@
       <c r="G15" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="20" t="s">
         <v>113</v>
       </c>
@@ -2609,8 +2840,8 @@
       <c r="M15" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N15" s="31"/>
-      <c r="O15" s="28"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="30"/>
       <c r="P15" s="9" t="s">
         <v>113</v>
       </c>
@@ -2629,27 +2860,51 @@
       <c r="U15" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V15" s="28"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="9"/>
-      <c r="AH15" s="9"/>
-      <c r="AI15" s="9"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI15" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ15" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
@@ -2676,7 +2931,7 @@
       <c r="G16" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="30"/>
       <c r="I16" s="20" t="s">
         <v>113</v>
       </c>
@@ -2692,8 +2947,8 @@
       <c r="M16" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N16" s="31"/>
-      <c r="O16" s="28"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="30"/>
       <c r="P16" s="9" t="s">
         <v>113</v>
       </c>
@@ -2712,34 +2967,58 @@
       <c r="U16" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V16" s="28"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="22"/>
-      <c r="AG16" s="9"/>
-      <c r="AH16" s="9"/>
-      <c r="AI16" s="9"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC16" s="30"/>
+      <c r="AD16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI16" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ16" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="AL16" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="25"/>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="26"/>
+      <c r="AL16" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="28"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
@@ -2761,7 +3040,7 @@
       <c r="G17" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="30"/>
       <c r="I17" s="20" t="s">
         <v>113</v>
       </c>
@@ -2777,8 +3056,8 @@
       <c r="M17" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N17" s="31"/>
-      <c r="O17" s="28"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="30"/>
       <c r="P17" s="9" t="s">
         <v>113</v>
       </c>
@@ -2797,23 +3076,47 @@
       <c r="U17" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V17" s="28"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="9"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="9"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="9"/>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="9"/>
-      <c r="AH17" s="9"/>
-      <c r="AI17" s="9"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC17" s="30"/>
+      <c r="AD17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI17" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ17" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
@@ -2852,7 +3155,7 @@
       <c r="G18" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="30"/>
       <c r="I18" s="20" t="s">
         <v>113</v>
       </c>
@@ -2868,8 +3171,8 @@
       <c r="M18" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N18" s="31"/>
-      <c r="O18" s="28"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="30"/>
       <c r="P18" s="9" t="s">
         <v>113</v>
       </c>
@@ -2888,23 +3191,47 @@
       <c r="U18" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V18" s="28"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="9"/>
-      <c r="AH18" s="9"/>
-      <c r="AI18" s="9"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI18" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ18" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
@@ -2946,7 +3273,7 @@
       <c r="G19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="30"/>
       <c r="I19" s="20" t="s">
         <v>113</v>
       </c>
@@ -2962,8 +3289,8 @@
       <c r="M19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N19" s="31"/>
-      <c r="O19" s="28"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="30"/>
       <c r="P19" s="9" t="s">
         <v>113</v>
       </c>
@@ -2974,7 +3301,7 @@
         <v>113</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>113</v>
@@ -2982,27 +3309,51 @@
       <c r="U19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V19" s="28"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="22"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="22"/>
-      <c r="AG19" s="9"/>
-      <c r="AH19" s="9"/>
-      <c r="AI19" s="9"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI19" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ19" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>19</v>
@@ -3040,7 +3391,7 @@
       <c r="G20" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="20" t="s">
         <v>114</v>
       </c>
@@ -3056,8 +3407,8 @@
       <c r="M20" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N20" s="31"/>
-      <c r="O20" s="28"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="30"/>
       <c r="P20" s="9" t="s">
         <v>113</v>
       </c>
@@ -3076,27 +3427,51 @@
       <c r="U20" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V20" s="28"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="22"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="22"/>
-      <c r="AG20" s="9"/>
-      <c r="AH20" s="9"/>
-      <c r="AI20" s="9"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI20" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ20" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL20" s="5" t="s">
         <v>15</v>
@@ -3134,7 +3509,7 @@
       <c r="G21" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H21" s="28"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="20" t="s">
         <v>113</v>
       </c>
@@ -3150,8 +3525,8 @@
       <c r="M21" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="N21" s="31"/>
-      <c r="O21" s="28"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="30"/>
       <c r="P21" s="9" t="s">
         <v>114</v>
       </c>
@@ -3170,27 +3545,51 @@
       <c r="U21" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V21" s="28"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="22"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="9"/>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="9"/>
-      <c r="AH21" s="9"/>
-      <c r="AI21" s="9"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC21" s="30"/>
+      <c r="AD21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI21" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ21" s="5">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3213,7 +3612,7 @@
       <c r="G22" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H22" s="28"/>
+      <c r="H22" s="30"/>
       <c r="I22" s="20" t="s">
         <v>113</v>
       </c>
@@ -3229,8 +3628,8 @@
       <c r="M22" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N22" s="31"/>
-      <c r="O22" s="28"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="30"/>
       <c r="P22" s="9" t="s">
         <v>113</v>
       </c>
@@ -3249,23 +3648,47 @@
       <c r="U22" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V22" s="28"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="9"/>
-      <c r="AH22" s="9"/>
-      <c r="AI22" s="9"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI22" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ22" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
@@ -3292,7 +3715,7 @@
       <c r="G23" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H23" s="28"/>
+      <c r="H23" s="30"/>
       <c r="I23" s="20" t="s">
         <v>113</v>
       </c>
@@ -3308,8 +3731,8 @@
       <c r="M23" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N23" s="31"/>
-      <c r="O23" s="28"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="30"/>
       <c r="P23" s="9" t="s">
         <v>113</v>
       </c>
@@ -3328,23 +3751,47 @@
       <c r="U23" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V23" s="28"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="9"/>
-      <c r="AH23" s="9"/>
-      <c r="AI23" s="9"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI23" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ23" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
@@ -3371,7 +3818,7 @@
       <c r="G24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H24" s="28"/>
+      <c r="H24" s="30"/>
       <c r="I24" s="20" t="s">
         <v>113</v>
       </c>
@@ -3387,8 +3834,8 @@
       <c r="M24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N24" s="31"/>
-      <c r="O24" s="28"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="30"/>
       <c r="P24" s="9" t="s">
         <v>113</v>
       </c>
@@ -3399,35 +3846,59 @@
         <v>113</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="V24" s="28"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="9"/>
-      <c r="AE24" s="9"/>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="9"/>
-      <c r="AH24" s="9"/>
-      <c r="AI24" s="9"/>
+        <v>115</v>
+      </c>
+      <c r="V24" s="30"/>
+      <c r="W24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="X24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI24" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ24" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3450,7 +3921,7 @@
       <c r="G25" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H25" s="28"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="20" t="s">
         <v>113</v>
       </c>
@@ -3466,8 +3937,8 @@
       <c r="M25" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N25" s="31"/>
-      <c r="O25" s="28"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="30"/>
       <c r="P25" s="9" t="s">
         <v>113</v>
       </c>
@@ -3486,27 +3957,51 @@
       <c r="U25" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V25" s="28"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="9"/>
-      <c r="AE25" s="9"/>
-      <c r="AF25" s="22"/>
-      <c r="AG25" s="9"/>
-      <c r="AH25" s="9"/>
-      <c r="AI25" s="9"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI25" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ25" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3529,7 +4024,7 @@
       <c r="G26" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="28"/>
+      <c r="H26" s="30"/>
       <c r="I26" s="20" t="s">
         <v>115</v>
       </c>
@@ -3545,8 +4040,8 @@
       <c r="M26" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="N26" s="31"/>
-      <c r="O26" s="28"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="30"/>
       <c r="P26" s="9" t="s">
         <v>115</v>
       </c>
@@ -3565,23 +4060,47 @@
       <c r="U26" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V26" s="28"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-      <c r="AF26" s="22"/>
-      <c r="AG26" s="9"/>
-      <c r="AH26" s="9"/>
-      <c r="AI26" s="9"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI26" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ26" s="5">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
@@ -3608,7 +4127,7 @@
       <c r="G27" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="28"/>
+      <c r="H27" s="30"/>
       <c r="I27" s="20" t="s">
         <v>113</v>
       </c>
@@ -3624,8 +4143,8 @@
       <c r="M27" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N27" s="31"/>
-      <c r="O27" s="28"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="30"/>
       <c r="P27" s="9" t="s">
         <v>113</v>
       </c>
@@ -3644,23 +4163,47 @@
       <c r="U27" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V27" s="28"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="9"/>
-      <c r="AE27" s="9"/>
-      <c r="AF27" s="22"/>
-      <c r="AG27" s="9"/>
-      <c r="AH27" s="9"/>
-      <c r="AI27" s="9"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI27" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ27" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
@@ -3687,7 +4230,7 @@
       <c r="G28" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H28" s="28"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="20" t="s">
         <v>114</v>
       </c>
@@ -3703,8 +4246,8 @@
       <c r="M28" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="N28" s="31"/>
-      <c r="O28" s="28"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="30"/>
       <c r="P28" s="9" t="s">
         <v>114</v>
       </c>
@@ -3715,35 +4258,59 @@
         <v>114</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="V28" s="28"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="9"/>
-      <c r="AF28" s="22"/>
-      <c r="AG28" s="9"/>
-      <c r="AH28" s="9"/>
-      <c r="AI28" s="9"/>
+        <v>114</v>
+      </c>
+      <c r="V28" s="30"/>
+      <c r="W28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI28" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ28" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3766,7 +4333,7 @@
       <c r="G29" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="28"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="20" t="s">
         <v>113</v>
       </c>
@@ -3782,8 +4349,8 @@
       <c r="M29" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N29" s="31"/>
-      <c r="O29" s="28"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="30"/>
       <c r="P29" s="9" t="s">
         <v>114</v>
       </c>
@@ -3794,7 +4361,7 @@
         <v>114</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>113</v>
@@ -3802,27 +4369,51 @@
       <c r="U29" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V29" s="28"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="22"/>
-      <c r="Z29" s="9"/>
-      <c r="AA29" s="9"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="9"/>
-      <c r="AE29" s="9"/>
-      <c r="AF29" s="22"/>
-      <c r="AG29" s="9"/>
-      <c r="AH29" s="9"/>
-      <c r="AI29" s="9"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI29" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ29" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -3845,7 +4436,7 @@
       <c r="G30" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H30" s="29"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="20" t="s">
         <v>113</v>
       </c>
@@ -3861,8 +4452,8 @@
       <c r="M30" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="N30" s="32"/>
-      <c r="O30" s="29"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="31"/>
       <c r="P30" s="9" t="s">
         <v>113</v>
       </c>
@@ -3881,23 +4472,47 @@
       <c r="U30" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V30" s="29"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="29"/>
-      <c r="AD30" s="9"/>
-      <c r="AE30" s="9"/>
-      <c r="AF30" s="22"/>
-      <c r="AG30" s="9"/>
-      <c r="AH30" s="9"/>
-      <c r="AI30" s="9"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI30" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ30" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
@@ -3906,6 +4521,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="H5:H30"/>
+    <mergeCell ref="O5:O30"/>
+    <mergeCell ref="V5:V30"/>
+    <mergeCell ref="AC5:AC30"/>
+    <mergeCell ref="N5:N30"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="AJ3:AJ4"/>
@@ -3916,25 +4538,18 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="H5:H30"/>
-    <mergeCell ref="O5:O30"/>
-    <mergeCell ref="V5:V30"/>
-    <mergeCell ref="AC5:AC30"/>
-    <mergeCell ref="N5:N30"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:AI4 F5:O5 T5:V5 AC5 P5:U30 W5:AB30 AD5:AI30 F6:G30 I6:M30">
+  <conditionalFormatting sqref="F3:AI4 F5:O5 T5:V5 AC5 P5:U30 F6:G30 I6:M30 W5:AB30 AD5:AI30">
     <cfRule type="expression" dxfId="31" priority="1">
       <formula>F$4=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI5 F6:G30 I6:M30 P6:U30 W6:X30 Z6:AB30 AD6:AE30 AG6:AI30 AL4:AM4">
+  <conditionalFormatting sqref="F6:G30 I6:M30 P6:U30 AL4:AM4 W6:AB30 F3:AI5 AD6:AI30">
     <cfRule type="expression" dxfId="30" priority="16">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AI5 F6:G30 I6:M30 P6:U30 W6:X30 Z6:AB30 AD6:AE30 AG6:AI30">
+  <conditionalFormatting sqref="F6:G30 I6:M30 P6:U30 W6:AB30 F5:AI5 AD6:AI30">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -4000,7 +4615,7 @@
     <col min="10" max="10" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -4028,101 +4643,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
+      <c r="A2" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -4245,25 +4860,25 @@
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AJ3" s="35" t="s">
+      <c r="AJ3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="24" t="s">
+      <c r="AL3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="25"/>
+      <c r="AM3" s="26"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="19">
         <v>45597</v>
       </c>
@@ -4354,8 +4969,8 @@
       <c r="AI4" s="19">
         <v>45626</v>
       </c>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4385,7 +5000,7 @@
       <c r="G5" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="29" t="s">
         <v>112</v>
       </c>
       <c r="I5" s="20" t="s">
@@ -4406,7 +5021,7 @@
       <c r="N5" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="O5" s="29" t="s">
         <v>112</v>
       </c>
       <c r="P5" s="9" t="s">
@@ -4427,27 +5042,51 @@
       <c r="U5" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="V5" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="27" t="s">
+      <c r="W5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC5" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="23"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
+      <c r="AD5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ5" s="5">
         <f t="shared" ref="AJ5:AJ30" si="1">COUNTIF(F5:AI5,"P")</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK30" si="2">COUNTIF(F5:AI5,"A")</f>
@@ -4484,7 +5123,7 @@
       <c r="G6" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="28"/>
+      <c r="H6" s="30"/>
       <c r="I6" s="20" t="s">
         <v>113</v>
       </c>
@@ -4501,7 +5140,7 @@
         <v>113</v>
       </c>
       <c r="N6" s="38"/>
-      <c r="O6" s="28"/>
+      <c r="O6" s="30"/>
       <c r="P6" s="9" t="s">
         <v>113</v>
       </c>
@@ -4520,23 +5159,47 @@
       <c r="U6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V6" s="28"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ6" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
@@ -4571,7 +5234,7 @@
       <c r="G7" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H7" s="28"/>
+      <c r="H7" s="30"/>
       <c r="I7" s="20" t="s">
         <v>113</v>
       </c>
@@ -4588,7 +5251,7 @@
         <v>113</v>
       </c>
       <c r="N7" s="38"/>
-      <c r="O7" s="28"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="9" t="s">
         <v>113</v>
       </c>
@@ -4605,29 +5268,53 @@
         <v>113</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="V7" s="28"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="23"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
+        <v>114</v>
+      </c>
+      <c r="V7" s="30"/>
+      <c r="W7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ7" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
@@ -4654,7 +5341,7 @@
       <c r="G8" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="30"/>
       <c r="I8" s="20" t="s">
         <v>113</v>
       </c>
@@ -4671,7 +5358,7 @@
         <v>113</v>
       </c>
       <c r="N8" s="38"/>
-      <c r="O8" s="28"/>
+      <c r="O8" s="30"/>
       <c r="P8" s="9" t="s">
         <v>113</v>
       </c>
@@ -4688,36 +5375,60 @@
         <v>113</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="V8" s="28"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
-      <c r="AI8" s="9"/>
+        <v>114</v>
+      </c>
+      <c r="V8" s="30"/>
+      <c r="W8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ8" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AL8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="25"/>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="26"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="28"/>
     </row>
     <row r="9" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
@@ -4739,7 +5450,7 @@
       <c r="G9" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="20" t="s">
         <v>115</v>
       </c>
@@ -4756,7 +5467,7 @@
         <v>115</v>
       </c>
       <c r="N9" s="38"/>
-      <c r="O9" s="28"/>
+      <c r="O9" s="30"/>
       <c r="P9" s="9" t="s">
         <v>115</v>
       </c>
@@ -4767,35 +5478,59 @@
         <v>115</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="V9" s="28"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="23"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
-      <c r="AI9" s="9"/>
+        <v>115</v>
+      </c>
+      <c r="V9" s="30"/>
+      <c r="W9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ9" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>12</v>
@@ -4830,7 +5565,7 @@
       <c r="G10" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="30"/>
       <c r="I10" s="20" t="s">
         <v>113</v>
       </c>
@@ -4847,7 +5582,7 @@
         <v>113</v>
       </c>
       <c r="N10" s="38"/>
-      <c r="O10" s="28"/>
+      <c r="O10" s="30"/>
       <c r="P10" s="9" t="s">
         <v>113</v>
       </c>
@@ -4866,23 +5601,47 @@
       <c r="U10" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V10" s="28"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="9"/>
-      <c r="AF10" s="23"/>
-      <c r="AG10" s="9"/>
-      <c r="AH10" s="9"/>
-      <c r="AI10" s="9"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI10" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ10" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
@@ -4924,7 +5683,7 @@
       <c r="G11" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="30"/>
       <c r="I11" s="20" t="s">
         <v>113</v>
       </c>
@@ -4941,7 +5700,7 @@
         <v>113</v>
       </c>
       <c r="N11" s="38"/>
-      <c r="O11" s="28"/>
+      <c r="O11" s="30"/>
       <c r="P11" s="9" t="s">
         <v>113</v>
       </c>
@@ -4958,36 +5717,60 @@
         <v>113</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="V11" s="28"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="23"/>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="9"/>
+        <v>114</v>
+      </c>
+      <c r="V11" s="30"/>
+      <c r="W11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG11" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI11" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ11" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AM11" s="10">
         <f>AJ6+AJ18</f>
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="AN11" s="10" t="e">
         <f>AJ5+AJ7+AJ8+AJ9+AJ11+AJ12+AJ13+AJ14+AJ15+AJ16+AJ17+#REF!+AJ19</f>
@@ -5018,7 +5801,7 @@
       <c r="G12" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="30"/>
       <c r="I12" s="20" t="s">
         <v>113</v>
       </c>
@@ -5035,7 +5818,7 @@
         <v>113</v>
       </c>
       <c r="N12" s="38"/>
-      <c r="O12" s="28"/>
+      <c r="O12" s="30"/>
       <c r="P12" s="9" t="s">
         <v>113</v>
       </c>
@@ -5054,34 +5837,58 @@
       <c r="U12" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V12" s="28"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="23"/>
-      <c r="AG12" s="9"/>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="9"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI12" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ12" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AM12" s="10">
         <f>AM11/AM10</f>
-        <v>4.6558704453441298E-2</v>
+        <v>7.8947368421052627E-2</v>
       </c>
       <c r="AN12" s="10" t="e">
         <f>AN11/AN10</f>
@@ -5112,7 +5919,7 @@
       <c r="G13" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="30"/>
       <c r="I13" s="20" t="s">
         <v>113</v>
       </c>
@@ -5129,7 +5936,7 @@
         <v>113</v>
       </c>
       <c r="N13" s="38"/>
-      <c r="O13" s="28"/>
+      <c r="O13" s="30"/>
       <c r="P13" s="9" t="s">
         <v>113</v>
       </c>
@@ -5140,7 +5947,7 @@
         <v>113</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T13" s="9" t="s">
         <v>113</v>
@@ -5148,27 +5955,51 @@
       <c r="U13" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V13" s="28"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AF13" s="23"/>
-      <c r="AG13" s="9"/>
-      <c r="AH13" s="9"/>
-      <c r="AI13" s="9"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC13" s="30"/>
+      <c r="AD13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI13" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ13" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL13" s="3"/>
       <c r="AM13" s="15"/>
@@ -5195,7 +6026,7 @@
       <c r="G14" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="30"/>
       <c r="I14" s="20" t="s">
         <v>113</v>
       </c>
@@ -5212,7 +6043,7 @@
         <v>113</v>
       </c>
       <c r="N14" s="38"/>
-      <c r="O14" s="28"/>
+      <c r="O14" s="30"/>
       <c r="P14" s="9" t="s">
         <v>113</v>
       </c>
@@ -5231,23 +6062,47 @@
       <c r="U14" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V14" s="28"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="9"/>
-      <c r="AH14" s="9"/>
-      <c r="AI14" s="9"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI14" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ14" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
@@ -5278,7 +6133,7 @@
       <c r="G15" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="20" t="s">
         <v>113</v>
       </c>
@@ -5295,7 +6150,7 @@
         <v>113</v>
       </c>
       <c r="N15" s="38"/>
-      <c r="O15" s="28"/>
+      <c r="O15" s="30"/>
       <c r="P15" s="9" t="s">
         <v>113</v>
       </c>
@@ -5306,7 +6161,7 @@
         <v>113</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>113</v>
@@ -5314,27 +6169,51 @@
       <c r="U15" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V15" s="28"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="23"/>
-      <c r="AG15" s="9"/>
-      <c r="AH15" s="9"/>
-      <c r="AI15" s="9"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI15" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ15" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
@@ -5361,7 +6240,7 @@
       <c r="G16" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="30"/>
       <c r="I16" s="20" t="s">
         <v>113</v>
       </c>
@@ -5378,7 +6257,7 @@
         <v>113</v>
       </c>
       <c r="N16" s="38"/>
-      <c r="O16" s="28"/>
+      <c r="O16" s="30"/>
       <c r="P16" s="9" t="s">
         <v>113</v>
       </c>
@@ -5397,34 +6276,58 @@
       <c r="U16" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V16" s="28"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="9"/>
-      <c r="AH16" s="9"/>
-      <c r="AI16" s="9"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC16" s="30"/>
+      <c r="AD16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI16" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ16" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="24" t="s">
+      <c r="AL16" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="25"/>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="26"/>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="28"/>
     </row>
     <row r="17" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
@@ -5446,7 +6349,7 @@
       <c r="G17" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="30"/>
       <c r="I17" s="20" t="s">
         <v>113</v>
       </c>
@@ -5463,7 +6366,7 @@
         <v>113</v>
       </c>
       <c r="N17" s="38"/>
-      <c r="O17" s="28"/>
+      <c r="O17" s="30"/>
       <c r="P17" s="9" t="s">
         <v>113</v>
       </c>
@@ -5482,23 +6385,47 @@
       <c r="U17" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V17" s="28"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="9"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="9"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="9"/>
-      <c r="AF17" s="23"/>
-      <c r="AG17" s="9"/>
-      <c r="AH17" s="9"/>
-      <c r="AI17" s="9"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC17" s="30"/>
+      <c r="AD17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI17" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ17" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
@@ -5537,7 +6464,7 @@
       <c r="G18" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="30"/>
       <c r="I18" s="20" t="s">
         <v>113</v>
       </c>
@@ -5554,7 +6481,7 @@
         <v>113</v>
       </c>
       <c r="N18" s="38"/>
-      <c r="O18" s="28"/>
+      <c r="O18" s="30"/>
       <c r="P18" s="9" t="s">
         <v>113</v>
       </c>
@@ -5573,27 +6500,51 @@
       <c r="U18" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V18" s="28"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="23"/>
-      <c r="AG18" s="9"/>
-      <c r="AH18" s="9"/>
-      <c r="AI18" s="9"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI18" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ18" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AL18" s="5" t="s">
         <v>16</v>
@@ -5631,7 +6582,7 @@
       <c r="G19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="30"/>
       <c r="I19" s="20" t="s">
         <v>113</v>
       </c>
@@ -5648,7 +6599,7 @@
         <v>113</v>
       </c>
       <c r="N19" s="38"/>
-      <c r="O19" s="28"/>
+      <c r="O19" s="30"/>
       <c r="P19" s="9" t="s">
         <v>113</v>
       </c>
@@ -5667,34 +6618,58 @@
       <c r="U19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V19" s="28"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="23"/>
-      <c r="AG19" s="9"/>
-      <c r="AH19" s="9"/>
-      <c r="AI19" s="9"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG19" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI19" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ19" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AM19" s="10">
         <f>AM18-AM11</f>
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="AN19" s="10" t="e">
         <f>AN18-AN11</f>
@@ -5725,7 +6700,7 @@
       <c r="G20" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="20" t="s">
         <v>113</v>
       </c>
@@ -5742,7 +6717,7 @@
         <v>113</v>
       </c>
       <c r="N20" s="38"/>
-      <c r="O20" s="28"/>
+      <c r="O20" s="30"/>
       <c r="P20" s="9" t="s">
         <v>113</v>
       </c>
@@ -5761,34 +6736,58 @@
       <c r="U20" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V20" s="28"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="23"/>
-      <c r="AG20" s="9"/>
-      <c r="AH20" s="9"/>
-      <c r="AI20" s="9"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI20" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ20" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AM20" s="18">
         <f>AM19/AM18</f>
-        <v>0.95344129554655865</v>
+        <v>0.92105263157894735</v>
       </c>
       <c r="AN20" s="18" t="e">
         <f>AN19/AN18</f>
@@ -5819,7 +6818,7 @@
       <c r="G21" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="28"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="20" t="s">
         <v>113</v>
       </c>
@@ -5836,7 +6835,7 @@
         <v>113</v>
       </c>
       <c r="N21" s="38"/>
-      <c r="O21" s="28"/>
+      <c r="O21" s="30"/>
       <c r="P21" s="9" t="s">
         <v>113</v>
       </c>
@@ -5855,23 +6854,47 @@
       <c r="U21" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V21" s="28"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="9"/>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="23"/>
-      <c r="AG21" s="9"/>
-      <c r="AH21" s="9"/>
-      <c r="AI21" s="9"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC21" s="30"/>
+      <c r="AD21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI21" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ21" s="5">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
@@ -5898,7 +6921,7 @@
       <c r="G22" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H22" s="28"/>
+      <c r="H22" s="30"/>
       <c r="I22" s="20" t="s">
         <v>113</v>
       </c>
@@ -5915,7 +6938,7 @@
         <v>113</v>
       </c>
       <c r="N22" s="38"/>
-      <c r="O22" s="28"/>
+      <c r="O22" s="30"/>
       <c r="P22" s="9" t="s">
         <v>113</v>
       </c>
@@ -5926,7 +6949,7 @@
         <v>113</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>113</v>
@@ -5934,27 +6957,51 @@
       <c r="U22" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V22" s="28"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="23"/>
-      <c r="AG22" s="9"/>
-      <c r="AH22" s="9"/>
-      <c r="AI22" s="9"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA22" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF22" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI22" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ22" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -5977,7 +7024,7 @@
       <c r="G23" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H23" s="28"/>
+      <c r="H23" s="30"/>
       <c r="I23" s="20" t="s">
         <v>113</v>
       </c>
@@ -5994,7 +7041,7 @@
         <v>113</v>
       </c>
       <c r="N23" s="38"/>
-      <c r="O23" s="28"/>
+      <c r="O23" s="30"/>
       <c r="P23" s="9" t="s">
         <v>113</v>
       </c>
@@ -6008,32 +7055,56 @@
         <v>113</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="U23" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V23" s="28"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="23"/>
-      <c r="AG23" s="9"/>
-      <c r="AH23" s="9"/>
-      <c r="AI23" s="9"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI23" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ23" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6042,7 +7113,7 @@
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>33</v>
@@ -6056,7 +7127,7 @@
       <c r="G24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H24" s="28"/>
+      <c r="H24" s="30"/>
       <c r="I24" s="20" t="s">
         <v>113</v>
       </c>
@@ -6073,7 +7144,7 @@
         <v>113</v>
       </c>
       <c r="N24" s="38"/>
-      <c r="O24" s="28"/>
+      <c r="O24" s="30"/>
       <c r="P24" s="9" t="s">
         <v>113</v>
       </c>
@@ -6092,23 +7163,47 @@
       <c r="U24" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V24" s="28"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="9"/>
-      <c r="AE24" s="9"/>
-      <c r="AF24" s="23"/>
-      <c r="AG24" s="9"/>
-      <c r="AH24" s="9"/>
-      <c r="AI24" s="9"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI24" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ24" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
@@ -6121,7 +7216,7 @@
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>38</v>
@@ -6135,7 +7230,7 @@
       <c r="G25" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H25" s="28"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="20" t="s">
         <v>113</v>
       </c>
@@ -6152,7 +7247,7 @@
         <v>113</v>
       </c>
       <c r="N25" s="38"/>
-      <c r="O25" s="28"/>
+      <c r="O25" s="30"/>
       <c r="P25" s="9" t="s">
         <v>113</v>
       </c>
@@ -6166,32 +7261,56 @@
         <v>113</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="U25" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V25" s="28"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="9"/>
-      <c r="AE25" s="9"/>
-      <c r="AF25" s="23"/>
-      <c r="AG25" s="9"/>
-      <c r="AH25" s="9"/>
-      <c r="AI25" s="9"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI25" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ25" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6214,7 +7333,7 @@
       <c r="G26" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="28"/>
+      <c r="H26" s="30"/>
       <c r="I26" s="20" t="s">
         <v>114</v>
       </c>
@@ -6231,7 +7350,7 @@
         <v>114</v>
       </c>
       <c r="N26" s="38"/>
-      <c r="O26" s="28"/>
+      <c r="O26" s="30"/>
       <c r="P26" s="9" t="s">
         <v>114</v>
       </c>
@@ -6250,27 +7369,51 @@
       <c r="U26" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V26" s="28"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-      <c r="AF26" s="23"/>
-      <c r="AG26" s="9"/>
-      <c r="AH26" s="9"/>
-      <c r="AI26" s="9"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI26" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ26" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6293,7 +7436,7 @@
       <c r="G27" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H27" s="28"/>
+      <c r="H27" s="30"/>
       <c r="I27" s="20" t="s">
         <v>113</v>
       </c>
@@ -6310,7 +7453,7 @@
         <v>114</v>
       </c>
       <c r="N27" s="38"/>
-      <c r="O27" s="28"/>
+      <c r="O27" s="30"/>
       <c r="P27" s="9" t="s">
         <v>113</v>
       </c>
@@ -6329,27 +7472,51 @@
       <c r="U27" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V27" s="28"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="9"/>
-      <c r="AE27" s="9"/>
-      <c r="AF27" s="23"/>
-      <c r="AG27" s="9"/>
-      <c r="AH27" s="9"/>
-      <c r="AI27" s="9"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X27" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z27" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI27" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ27" s="5">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6372,7 +7539,7 @@
       <c r="G28" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H28" s="28"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="20" t="s">
         <v>115</v>
       </c>
@@ -6386,10 +7553,10 @@
         <v>115</v>
       </c>
       <c r="M28" s="20" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N28" s="38"/>
-      <c r="O28" s="28"/>
+      <c r="O28" s="30"/>
       <c r="P28" s="9" t="s">
         <v>115</v>
       </c>
@@ -6400,7 +7567,7 @@
         <v>115</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>113</v>
@@ -6408,27 +7575,51 @@
       <c r="U28" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V28" s="28"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="9"/>
-      <c r="AF28" s="23"/>
-      <c r="AG28" s="9"/>
-      <c r="AH28" s="9"/>
-      <c r="AI28" s="9"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI28" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="AJ28" s="5">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:41" ht="16.5" x14ac:dyDescent="0.25">
@@ -6451,7 +7642,7 @@
       <c r="G29" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="28"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="20" t="s">
         <v>113</v>
       </c>
@@ -6468,7 +7659,7 @@
         <v>113</v>
       </c>
       <c r="N29" s="38"/>
-      <c r="O29" s="28"/>
+      <c r="O29" s="30"/>
       <c r="P29" s="9" t="s">
         <v>113</v>
       </c>
@@ -6487,23 +7678,47 @@
       <c r="U29" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V29" s="28"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="9"/>
-      <c r="AA29" s="9"/>
-      <c r="AB29" s="9"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="9"/>
-      <c r="AE29" s="9"/>
-      <c r="AF29" s="23"/>
-      <c r="AG29" s="9"/>
-      <c r="AH29" s="9"/>
-      <c r="AI29" s="9"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI29" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ29" s="5">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
@@ -6530,7 +7745,7 @@
       <c r="G30" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H30" s="29"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="20" t="s">
         <v>113</v>
       </c>
@@ -6547,7 +7762,7 @@
         <v>113</v>
       </c>
       <c r="N30" s="39"/>
-      <c r="O30" s="29"/>
+      <c r="O30" s="31"/>
       <c r="P30" s="9" t="s">
         <v>113</v>
       </c>
@@ -6566,27 +7781,51 @@
       <c r="U30" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="V30" s="29"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="29"/>
-      <c r="AD30" s="9"/>
-      <c r="AE30" s="9"/>
-      <c r="AF30" s="23"/>
-      <c r="AG30" s="9"/>
-      <c r="AH30" s="9"/>
-      <c r="AI30" s="9"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE30" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI30" s="9" t="s">
+        <v>113</v>
+      </c>
       <c r="AJ30" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
@@ -6599,6 +7838,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="N5:N30"/>
     <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="AL8:AO8"/>
     <mergeCell ref="AL16:AO16"/>
@@ -6615,14 +7855,13 @@
     <mergeCell ref="O5:O30"/>
     <mergeCell ref="V5:V30"/>
     <mergeCell ref="AC5:AC30"/>
-    <mergeCell ref="N5:N30"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:G30 I6:M30 W6:X30 Z6:AB30 AD6:AE30 AG6:AI30 F4:AI4">
+  <conditionalFormatting sqref="F6:G30 I6:M30 F4:AI4">
     <cfRule type="expression" dxfId="20" priority="29">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:G30 I6:M30 W6:X30 Z6:AB30 AD6:AE30 AG6:AI30">
+  <conditionalFormatting sqref="F6:G30 I6:M30">
     <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -6650,47 +7889,47 @@
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI4 F6:G30 I6:M30 W6:X30 Z6:AB30 AD6:AE30 AG6:AI30 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20">
+  <conditionalFormatting sqref="F3:AI4 F6:G30 I6:M30 AL4:AM4 AL5:AL6 AM9:AO9 AL9:AL12 AM17:AO17 AL17:AL20">
     <cfRule type="expression" dxfId="11" priority="30">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:U30">
-    <cfRule type="cellIs" dxfId="10" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="19">
+    <cfRule type="expression" dxfId="1" priority="19">
       <formula>IF(P$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="20">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>P$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:AI5">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="W6:AB30 V5:AI5 AD6:AI30">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>IF(V$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>V$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK30">
-    <cfRule type="expression" dxfId="0" priority="31">
+    <cfRule type="expression" dxfId="5" priority="31">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
